--- a/sample_files/malformed_data.xlsx
+++ b/sample_files/malformed_data.xlsx
@@ -465,79 +465,79 @@
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>String-30</t>
-        </is>
+      <c r="C2" t="n">
+        <v>89</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Some text</t>
+        </is>
+      </c>
       <c r="C3" t="n">
-        <v>0.3008727523583993</v>
+        <v>68</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Some text</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0.6120831456973551</v>
+        <v>0.1572775334783965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>String-44</t>
-        </is>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Some text</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.3820289676983751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>05/21/2025</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -545,19 +545,21 @@
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>0.1527066875456308</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>String-47</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>07-Apr-2025</t>
+          <t>Not a date</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -566,11 +568,11 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
@@ -580,26 +582,20 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Some text</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>String-92</t>
-        </is>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>0.2809022155174209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>07-Apr-2025</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -607,21 +603,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>String-51</t>
-        </is>
+      <c r="C9" t="n">
+        <v>0.3886207072394381</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -630,18 +624,18 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0.8611734430075862</v>
+        <v>0.8922654127699942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -649,19 +643,21 @@
         <v>10</v>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>46</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>String-15</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -669,47 +665,41 @@
         <v>11</v>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>String-76</t>
-        </is>
+      <c r="C12" t="n">
+        <v>20</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>Not a date</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Some text</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>String-6</t>
+          <t>String-76</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07-Apr-2025</t>
+          <t>05/21/2025</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -717,19 +707,21 @@
         <v>13</v>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>0.5657258370635121</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>String-56</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>07-Apr-2025</t>
+          <t>05/21/2025</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -739,16 +731,16 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>String-64</t>
+          <t>String-54</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>05/21/2025</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>9</v>
@@ -758,20 +750,20 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Some text</t>
+        </is>
+      </c>
       <c r="C16" t="n">
-        <v>90</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>07-Apr-2025</t>
-        </is>
-      </c>
+        <v>0.4946741784265731</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -779,21 +771,15 @@
         <v>16</v>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>String-56</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>07-Apr-2025</t>
-        </is>
-      </c>
+      <c r="C17" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -802,66 +788,58 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0.06679892856125291</v>
+        <v>35</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>05/21/2025</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Some text</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>72</v>
+        <v>0.5279672291431216</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Some text</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -870,11 +848,11 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>0.3012478424094898</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
@@ -886,18 +864,18 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>59</v>
+        <v>0.7541671523296113</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -909,24 +887,34 @@
           <t>Some text</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>0.1242820685204922</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>String-54</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Not a date</t>
+        </is>
+      </c>
       <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
         <v>7</v>
-      </c>
-      <c r="F23" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Some text</t>
+        </is>
+      </c>
       <c r="C24" t="n">
-        <v>0.8888332445692084</v>
+        <v>25</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -934,7 +922,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
@@ -944,20 +932,24 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Some text</t>
+        </is>
+      </c>
       <c r="C25" t="n">
-        <v>62</v>
+        <v>0.7511878718088788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>07-Apr-2025</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -967,19 +959,19 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>String-38</t>
+          <t>String-33</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -987,8 +979,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>0.5293714130221691</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>String-55</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -996,10 +990,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1012,36 +1006,42 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>93</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>05/21/2025</t>
+        </is>
+      </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>String-72</t>
-        </is>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Some text</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.880500873413841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>05/21/2025</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1050,18 +1050,18 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0.6146039710939154</v>
+        <v>40</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1070,18 +1070,18 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -1090,42 +1090,34 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0.9184224237999215</v>
+        <v>0.2713473200732007</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>07-Apr-2025</t>
+          <t>Not a date</t>
         </is>
       </c>
       <c r="E32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" t="n">
         <v>3</v>
-      </c>
-      <c r="F32" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Some text</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>37</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>04/07/2025</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -1134,15 +1126,15 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>07-Apr-2025</t>
+          <t>Not a date</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -1152,40 +1144,50 @@
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>37</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Some text</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>String-18</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>Not a date</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Some text</t>
+        </is>
+      </c>
       <c r="C36" t="n">
-        <v>30</v>
+        <v>0.3821242092471062</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>07-Apr-2025</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1193,21 +1195,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>String-78</t>
-        </is>
+      <c r="C37" t="n">
+        <v>0.9476659353726695</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>5</v>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -1216,18 +1216,18 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -1235,21 +1235,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>String-93</t>
-        </is>
+      <c r="C39" t="n">
+        <v>32</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>05/21/2025</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1257,21 +1255,15 @@
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>String-85</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>07-Apr-2025</t>
-        </is>
-      </c>
+      <c r="C40" t="n">
+        <v>0.3473709487785825</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1281,19 +1273,19 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>String-90</t>
+          <t>String-81</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1301,10 +1293,8 @@
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>String-15</t>
-        </is>
+      <c r="C42" t="n">
+        <v>0.7012168490514307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1312,7 +1302,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F42" t="n">
         <v>4</v>
@@ -1324,14 +1314,14 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>64</v>
+        <v>0.0562991484987172</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" t="n">
         <v>8</v>
-      </c>
-      <c r="F43" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -1339,21 +1329,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>String-27</t>
-        </is>
+      <c r="C44" t="n">
+        <v>45</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1366,31 +1354,29 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>05/21/2025</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Some text</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0.2982684933963186</v>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>String-55</t>
+        </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1398,10 +1384,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -1414,18 +1400,18 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.6696130823248376</v>
+        <v>0.5104707821340829</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>07-Apr-2025</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -1439,19 +1425,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>String-6</t>
+          <t>String-55</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -1460,18 +1446,18 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.732946782580263</v>
+        <v>0.8831577248620024</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -1479,30 +1465,32 @@
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>String-5</t>
-        </is>
+      <c r="C50" t="n">
+        <v>100</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>05/21/2025</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Some text</t>
+        </is>
+      </c>
       <c r="C51" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1510,15 +1498,15 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1526,103 +1514,99 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>42</v>
+        <v>0.3821242092471062</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.1527066875456308</v>
+        <v>0.2713473200732007</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>07-Apr-2025</t>
+          <t>Not a date</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>8</v>
       </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>41</v>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>String-15</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Some text</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.3821242092471062</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>19</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Some text</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>05/21/2025</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>String-15</t>
-        </is>
+      <c r="C56" t="n">
+        <v>45</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Not a date</t>
+          <t>21-May-2025</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>4</v>
